--- a/FleetManagement/src/test/resources/TestData.xlsx
+++ b/FleetManagement/src/test/resources/TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vp671\git\repository\FleetManagemnet\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vp671\git\FleetManagemnet\FleetManagement\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD1C957-853F-4BE2-ACB5-11ECBD90063E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6858DFC9-D239-4698-ACA6-0711C1DFD7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8161A61B-8086-477D-8B1E-55D122633EED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8161A61B-8086-477D-8B1E-55D122633EED}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -264,13 +264,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -587,30 +586,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17FECE4-AD0F-475D-84AC-72B5639CE5BF}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -641,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>49</v>
       </c>
@@ -675,7 +674,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -709,7 +708,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -743,7 +742,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -777,7 +776,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -811,7 +810,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -845,16 +844,16 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C11" s="4"/>
     </row>
   </sheetData>
